--- a/src/uploads/excel-exports/case_report.xlsx
+++ b/src/uploads/excel-exports/case_report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="890" uniqueCount="329">
   <si>
     <t>Case Number</t>
   </si>
@@ -43,247 +43,961 @@
     <t>Created Date</t>
   </si>
   <si>
-    <t>00001030</t>
+    <t>00127431</t>
+  </si>
+  <si>
+    <t>New</t>
+  </si>
+  <si>
+    <t>Redo TCPA</t>
+  </si>
+  <si>
+    <t>Rideshare</t>
+  </si>
+  <si>
+    <t>Campaign_p</t>
+  </si>
+  <si>
+    <t>Medium Quality</t>
+  </si>
+  <si>
+    <t>Sranil Kamble</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>7472492328</t>
+  </si>
+  <si>
+    <t>08/04/2026 18:31</t>
+  </si>
+  <si>
+    <t>00127430</t>
+  </si>
+  <si>
+    <t>No TCPA</t>
+  </si>
+  <si>
+    <t>13237059550</t>
+  </si>
+  <si>
+    <t>08/04/2026 18:03</t>
+  </si>
+  <si>
+    <t>00127429</t>
+  </si>
+  <si>
+    <t>Sent</t>
+  </si>
+  <si>
+    <t>Signed</t>
+  </si>
+  <si>
+    <t>3236773231</t>
+  </si>
+  <si>
+    <t>08/04/2026 17:45</t>
+  </si>
+  <si>
+    <t>00127428</t>
+  </si>
+  <si>
+    <t>In progress</t>
+  </si>
+  <si>
+    <t>Callback</t>
+  </si>
+  <si>
+    <t>Rahil Sattar</t>
+  </si>
+  <si>
+    <t>7029317166</t>
+  </si>
+  <si>
+    <t>08/04/2026 17:27</t>
+  </si>
+  <si>
+    <t>00127427</t>
   </si>
   <si>
     <t>Closed</t>
   </si>
   <si>
-    <t>Unreachable</t>
-  </si>
-  <si>
-    <t>Talcum</t>
-  </si>
-  <si>
-    <t>Campaign_p</t>
+    <t>On hold</t>
+  </si>
+  <si>
+    <t>Transfer</t>
+  </si>
+  <si>
+    <t>Kirti Pawar</t>
+  </si>
+  <si>
+    <t>2516436791</t>
+  </si>
+  <si>
+    <t>08/04/2026 17:25</t>
+  </si>
+  <si>
+    <t>00127426</t>
+  </si>
+  <si>
+    <t>No Answer</t>
+  </si>
+  <si>
+    <t>Pranit Bhalerao</t>
+  </si>
+  <si>
+    <t>9293909776</t>
+  </si>
+  <si>
+    <t>08/04/2026 17:21</t>
+  </si>
+  <si>
+    <t>00127424</t>
   </si>
   <si>
     <t>Low Quality</t>
   </si>
   <si>
-    <t>Sana Shaikh</t>
-  </si>
-  <si>
-    <t>N/A</t>
-  </si>
-  <si>
-    <t>3475517136</t>
-  </si>
-  <si>
-    <t>07/07/2023 13:20</t>
-  </si>
-  <si>
-    <t>00001031</t>
-  </si>
-  <si>
-    <t>Camp Lejeune</t>
-  </si>
-  <si>
-    <t>Sambhaji Shinde</t>
-  </si>
-  <si>
-    <t>7542452151</t>
-  </si>
-  <si>
-    <t>00001032</t>
-  </si>
-  <si>
-    <t>Accepted</t>
+    <t>Shubham Tayade</t>
+  </si>
+  <si>
+    <t>9019027428</t>
+  </si>
+  <si>
+    <t>08/04/2026 17:03</t>
+  </si>
+  <si>
+    <t>00127423</t>
+  </si>
+  <si>
+    <t>Anay Jagtap</t>
+  </si>
+  <si>
+    <t>7738851891</t>
+  </si>
+  <si>
+    <t>00127422</t>
+  </si>
+  <si>
+    <t>Fazle Shaikh</t>
+  </si>
+  <si>
+    <t>7732199059</t>
+  </si>
+  <si>
+    <t>08/04/2026 17:01</t>
+  </si>
+  <si>
+    <t>00127421</t>
+  </si>
+  <si>
+    <t>Disqualified</t>
+  </si>
+  <si>
+    <t>Prachi Yadav</t>
+  </si>
+  <si>
+    <t>6089613288</t>
+  </si>
+  <si>
+    <t>00127420</t>
+  </si>
+  <si>
+    <t>Ranjit Kaur</t>
+  </si>
+  <si>
+    <t>4355593145</t>
+  </si>
+  <si>
+    <t>08/04/2026 16:59</t>
+  </si>
+  <si>
+    <t>00127419</t>
+  </si>
+  <si>
+    <t>Ojas Panchasara</t>
+  </si>
+  <si>
+    <t>9855026715</t>
+  </si>
+  <si>
+    <t>08/04/2026 16:52</t>
+  </si>
+  <si>
+    <t>00127417</t>
+  </si>
+  <si>
+    <t>Shitala Prassad</t>
+  </si>
+  <si>
+    <t>7024687671</t>
+  </si>
+  <si>
+    <t>08/04/2026 16:09</t>
+  </si>
+  <si>
+    <t>00127416</t>
+  </si>
+  <si>
+    <t>7069151560</t>
+  </si>
+  <si>
+    <t>00127415</t>
+  </si>
+  <si>
+    <t>3478447684</t>
+  </si>
+  <si>
+    <t>00127414</t>
+  </si>
+  <si>
+    <t>Prasad Sanjay Giramkar</t>
+  </si>
+  <si>
+    <t>3213051218</t>
+  </si>
+  <si>
+    <t>08/04/2026 16:07</t>
+  </si>
+  <si>
+    <t>00127413</t>
+  </si>
+  <si>
+    <t>VM</t>
+  </si>
+  <si>
+    <t>9517288366</t>
+  </si>
+  <si>
+    <t>08/04/2026 15:54</t>
+  </si>
+  <si>
+    <t>00127412</t>
+  </si>
+  <si>
+    <t>High Quality</t>
+  </si>
+  <si>
+    <t>Vishal Sukheja</t>
+  </si>
+  <si>
+    <t>2144572436</t>
+  </si>
+  <si>
+    <t>08/04/2026 15:53</t>
+  </si>
+  <si>
+    <t>00127411</t>
+  </si>
+  <si>
+    <t>Austin Joseph</t>
+  </si>
+  <si>
+    <t>8552526955</t>
+  </si>
+  <si>
+    <t>08/04/2026 15:37</t>
+  </si>
+  <si>
+    <t>00127410</t>
+  </si>
+  <si>
+    <t>Rutuja Uttekar</t>
+  </si>
+  <si>
+    <t>7023132933</t>
+  </si>
+  <si>
+    <t>08/04/2026 15:30</t>
+  </si>
+  <si>
+    <t>00127409</t>
+  </si>
+  <si>
+    <t>Rushabh Vankalas</t>
+  </si>
+  <si>
+    <t>7253262833</t>
+  </si>
+  <si>
+    <t>08/04/2026 15:29</t>
+  </si>
+  <si>
+    <t>00127408</t>
+  </si>
+  <si>
+    <t>4245034821</t>
+  </si>
+  <si>
+    <t>08/04/2026 15:24</t>
+  </si>
+  <si>
+    <t>00127407</t>
+  </si>
+  <si>
+    <t>6148869464</t>
+  </si>
+  <si>
+    <t>08/04/2026 15:23</t>
+  </si>
+  <si>
+    <t>00127406</t>
+  </si>
+  <si>
+    <t>Depo Provera</t>
+  </si>
+  <si>
+    <t>2148933523</t>
+  </si>
+  <si>
+    <t>08/04/2026 15:16</t>
+  </si>
+  <si>
+    <t>00127405</t>
+  </si>
+  <si>
+    <t>Sohail Sayyed</t>
+  </si>
+  <si>
+    <t>3106968772</t>
+  </si>
+  <si>
+    <t>08/04/2026 15:10</t>
+  </si>
+  <si>
+    <t>00127404</t>
+  </si>
+  <si>
+    <t>Snehal Pawar</t>
+  </si>
+  <si>
+    <t>7733318871</t>
+  </si>
+  <si>
+    <t>08/04/2026 15:08</t>
+  </si>
+  <si>
+    <t>00127402</t>
+  </si>
+  <si>
+    <t>7606687852</t>
+  </si>
+  <si>
+    <t>08/04/2026 15:06</t>
+  </si>
+  <si>
+    <t>00127401</t>
+  </si>
+  <si>
+    <t>3124593217</t>
+  </si>
+  <si>
+    <t>08/04/2026 15:05</t>
+  </si>
+  <si>
+    <t>00127400</t>
+  </si>
+  <si>
+    <t>9097623572</t>
+  </si>
+  <si>
+    <t>00127399</t>
+  </si>
+  <si>
+    <t>Vivek Pawar</t>
+  </si>
+  <si>
+    <t>9293294511</t>
+  </si>
+  <si>
+    <t>08/04/2026 14:59</t>
+  </si>
+  <si>
+    <t>00127398</t>
+  </si>
+  <si>
+    <t>Sourabh Bisht</t>
+  </si>
+  <si>
+    <t>2169035430</t>
+  </si>
+  <si>
+    <t>08/04/2026 14:51</t>
+  </si>
+  <si>
+    <t>00127397</t>
+  </si>
+  <si>
+    <t>2139846187</t>
+  </si>
+  <si>
+    <t>08/04/2026 14:48</t>
+  </si>
+  <si>
+    <t>00127396</t>
+  </si>
+  <si>
+    <t>Campaign_k</t>
+  </si>
+  <si>
+    <t>International Media Group</t>
+  </si>
+  <si>
+    <t>8636055041</t>
+  </si>
+  <si>
+    <t>08/04/2026 14:41</t>
+  </si>
+  <si>
+    <t>00127395</t>
+  </si>
+  <si>
+    <t>9148301683</t>
+  </si>
+  <si>
+    <t>00127394</t>
+  </si>
+  <si>
+    <t>6693496337</t>
+  </si>
+  <si>
+    <t>08/04/2026 14:39</t>
+  </si>
+  <si>
+    <t>00127393</t>
+  </si>
+  <si>
+    <t>6464790701</t>
+  </si>
+  <si>
+    <t>00127392</t>
+  </si>
+  <si>
+    <t>Comercial IMG</t>
+  </si>
+  <si>
+    <t>3235367240</t>
+  </si>
+  <si>
+    <t>08/04/2026 14:36</t>
+  </si>
+  <si>
+    <t>00127391</t>
+  </si>
+  <si>
+    <t>12624617583</t>
+  </si>
+  <si>
+    <t>08/04/2026 14:23</t>
+  </si>
+  <si>
+    <t>00127390</t>
+  </si>
+  <si>
+    <t>4073121422</t>
+  </si>
+  <si>
+    <t>08/04/2026 14:19</t>
+  </si>
+  <si>
+    <t>00127389</t>
+  </si>
+  <si>
+    <t>Aditya Mishra</t>
+  </si>
+  <si>
+    <t>4042907375</t>
+  </si>
+  <si>
+    <t>08/04/2026 14:16</t>
+  </si>
+  <si>
+    <t>00127388</t>
+  </si>
+  <si>
+    <t>Sunshine Rigsby</t>
+  </si>
+  <si>
+    <t>9172723283</t>
+  </si>
+  <si>
+    <t>08/04/2026 14:13</t>
+  </si>
+  <si>
+    <t>00127387</t>
+  </si>
+  <si>
+    <t>On call</t>
+  </si>
+  <si>
+    <t>2149955202</t>
+  </si>
+  <si>
+    <t>08/04/2026 14:10</t>
+  </si>
+  <si>
+    <t>00127386</t>
+  </si>
+  <si>
+    <t>Do Not Call</t>
+  </si>
+  <si>
+    <t>2144891318</t>
+  </si>
+  <si>
+    <t>08/04/2026 14:09</t>
+  </si>
+  <si>
+    <t>00127385</t>
+  </si>
+  <si>
+    <t>7084778741</t>
+  </si>
+  <si>
+    <t>08/04/2026 14:08</t>
+  </si>
+  <si>
+    <t>00127384</t>
+  </si>
+  <si>
+    <t>9097892596</t>
+  </si>
+  <si>
+    <t>08/04/2026 14:05</t>
+  </si>
+  <si>
+    <t>00127383</t>
+  </si>
+  <si>
+    <t>2133778553</t>
+  </si>
+  <si>
+    <t>08/04/2026 14:02</t>
+  </si>
+  <si>
+    <t>00127382</t>
+  </si>
+  <si>
+    <t>5108070547</t>
+  </si>
+  <si>
+    <t>08/04/2026 13:51</t>
+  </si>
+  <si>
+    <t>00127381</t>
+  </si>
+  <si>
+    <t>Nitesh Bhalla</t>
+  </si>
+  <si>
+    <t>4703228469</t>
+  </si>
+  <si>
+    <t>08/04/2026 13:49</t>
+  </si>
+  <si>
+    <t>00127380</t>
+  </si>
+  <si>
+    <t>Danish Jahangir</t>
+  </si>
+  <si>
+    <t>7734084472</t>
+  </si>
+  <si>
+    <t>08/04/2026 13:47</t>
+  </si>
+  <si>
+    <t>00127379</t>
+  </si>
+  <si>
+    <t>Spam</t>
+  </si>
+  <si>
+    <t>3122277918</t>
+  </si>
+  <si>
+    <t>08/04/2026 13:36</t>
+  </si>
+  <si>
+    <t>00127378</t>
+  </si>
+  <si>
+    <t>Navid Jahangir</t>
+  </si>
+  <si>
+    <t>3239450969</t>
+  </si>
+  <si>
+    <t>08/04/2026 13:34</t>
+  </si>
+  <si>
+    <t>00127376</t>
+  </si>
+  <si>
+    <t>Shruja Ajmera</t>
+  </si>
+  <si>
+    <t>2146857073</t>
+  </si>
+  <si>
+    <t>08/04/2026 13:31</t>
+  </si>
+  <si>
+    <t>00127375</t>
+  </si>
+  <si>
+    <t>9514491130</t>
+  </si>
+  <si>
+    <t>08/04/2026 13:24</t>
+  </si>
+  <si>
+    <t>00127374</t>
+  </si>
+  <si>
+    <t>6466124706</t>
+  </si>
+  <si>
+    <t>08/04/2026 13:21</t>
+  </si>
+  <si>
+    <t>00127373</t>
+  </si>
+  <si>
+    <t>Vishal Gadhave</t>
+  </si>
+  <si>
+    <t>7252036399</t>
+  </si>
+  <si>
+    <t>08/04/2026 13:16</t>
+  </si>
+  <si>
+    <t>00127372</t>
+  </si>
+  <si>
+    <t>7024122287</t>
+  </si>
+  <si>
+    <t>08/04/2026 13:13</t>
+  </si>
+  <si>
+    <t>00127371</t>
+  </si>
+  <si>
+    <t>2139843377</t>
+  </si>
+  <si>
+    <t>08/04/2026 13:04</t>
+  </si>
+  <si>
+    <t>00127370</t>
+  </si>
+  <si>
+    <t>Fardin Shaikh</t>
+  </si>
+  <si>
+    <t>8168856462</t>
+  </si>
+  <si>
+    <t>08/04/2026 13:01</t>
+  </si>
+  <si>
+    <t>00127369</t>
+  </si>
+  <si>
+    <t>2135987320</t>
+  </si>
+  <si>
+    <t>08/04/2026 12:54</t>
+  </si>
+  <si>
+    <t>00127368</t>
+  </si>
+  <si>
+    <t>6469512486</t>
+  </si>
+  <si>
+    <t>08/04/2026 12:47</t>
+  </si>
+  <si>
+    <t>00127367</t>
+  </si>
+  <si>
+    <t>5046546623</t>
+  </si>
+  <si>
+    <t>08/04/2026 12:46</t>
+  </si>
+  <si>
+    <t>00127366</t>
+  </si>
+  <si>
+    <t>9166622993</t>
+  </si>
+  <si>
+    <t>08/04/2026 12:45</t>
+  </si>
+  <si>
+    <t>00127365</t>
+  </si>
+  <si>
+    <t>5416259785</t>
+  </si>
+  <si>
+    <t>08/04/2026 12:43</t>
+  </si>
+  <si>
+    <t>00127364</t>
+  </si>
+  <si>
+    <t>8182862437</t>
+  </si>
+  <si>
+    <t>08/04/2026 12:38</t>
+  </si>
+  <si>
+    <t>00127363</t>
+  </si>
+  <si>
+    <t>6576433619</t>
+  </si>
+  <si>
+    <t>08/04/2026 12:08</t>
+  </si>
+  <si>
+    <t>00127362</t>
+  </si>
+  <si>
+    <t>7023439238</t>
+  </si>
+  <si>
+    <t>08/04/2026 12:04</t>
+  </si>
+  <si>
+    <t>00127361</t>
+  </si>
+  <si>
+    <t>​Shreyash Pundalik Dhangar</t>
+  </si>
+  <si>
+    <t>9013378152</t>
+  </si>
+  <si>
+    <t>08/04/2026 12:01</t>
+  </si>
+  <si>
+    <t>00127360</t>
+  </si>
+  <si>
+    <t>3126875575</t>
+  </si>
+  <si>
+    <t>08/04/2026 12:00</t>
+  </si>
+  <si>
+    <t>00127358</t>
+  </si>
+  <si>
+    <t>3478429923</t>
+  </si>
+  <si>
+    <t>08/04/2026 11:30</t>
+  </si>
+  <si>
+    <t>00127357</t>
+  </si>
+  <si>
+    <t>To transfer</t>
+  </si>
+  <si>
+    <t>9719850875</t>
+  </si>
+  <si>
+    <t>08/04/2026 11:17</t>
+  </si>
+  <si>
+    <t>00127356</t>
+  </si>
+  <si>
+    <t>Nadeem Sajjan</t>
+  </si>
+  <si>
+    <t>7578195586</t>
+  </si>
+  <si>
+    <t>08/04/2026 11:12</t>
+  </si>
+  <si>
+    <t>00127355</t>
+  </si>
+  <si>
+    <t>4452059983</t>
+  </si>
+  <si>
+    <t>08/04/2026 11:03</t>
+  </si>
+  <si>
+    <t>00127354</t>
+  </si>
+  <si>
+    <t>2817147358</t>
+  </si>
+  <si>
+    <t>08/04/2026 11:01</t>
+  </si>
+  <si>
+    <t>00127353</t>
+  </si>
+  <si>
+    <t>6802225770</t>
+  </si>
+  <si>
+    <t>08/04/2026 10:57</t>
+  </si>
+  <si>
+    <t>00127352</t>
+  </si>
+  <si>
+    <t>4453049373</t>
+  </si>
+  <si>
+    <t>08/04/2026 10:37</t>
+  </si>
+  <si>
+    <t>00127351</t>
+  </si>
+  <si>
+    <t>Afaque Shaikh</t>
+  </si>
+  <si>
+    <t>7868175986</t>
+  </si>
+  <si>
+    <t>08/04/2026 10:30</t>
+  </si>
+  <si>
+    <t>00127350</t>
   </si>
   <si>
     <t>Naved Aslam</t>
   </si>
   <si>
-    <t>3128979445</t>
-  </si>
-  <si>
-    <t>00001033</t>
-  </si>
-  <si>
-    <t>Reject</t>
-  </si>
-  <si>
-    <t>Medium Quality</t>
-  </si>
-  <si>
-    <t>Kirti Pawar</t>
-  </si>
-  <si>
-    <t>5126738657</t>
-  </si>
-  <si>
-    <t>00001034</t>
-  </si>
-  <si>
-    <t>Agustin he</t>
-  </si>
-  <si>
-    <t>8703476094</t>
-  </si>
-  <si>
-    <t>00001035</t>
-  </si>
-  <si>
-    <t>Disqualified</t>
-  </si>
-  <si>
-    <t>Aziz Qureshi</t>
-  </si>
-  <si>
-    <t>15392863549</t>
-  </si>
-  <si>
-    <t>00001036</t>
-  </si>
-  <si>
-    <t>If criteria changes</t>
-  </si>
-  <si>
-    <t>Baby Formula</t>
-  </si>
-  <si>
-    <t>4048401573</t>
-  </si>
-  <si>
-    <t>00001037</t>
-  </si>
-  <si>
-    <t>7314993832</t>
-  </si>
-  <si>
-    <t>00001038</t>
-  </si>
-  <si>
-    <t>4043146391</t>
-  </si>
-  <si>
-    <t>00001039</t>
-  </si>
-  <si>
-    <t>9062502920</t>
-  </si>
-  <si>
-    <t>00001040</t>
-  </si>
-  <si>
-    <t>3144054564</t>
-  </si>
-  <si>
-    <t>00001041</t>
-  </si>
-  <si>
-    <t>7314370312</t>
-  </si>
-  <si>
-    <t>00001042</t>
-  </si>
-  <si>
-    <t>Returned to supplier</t>
-  </si>
-  <si>
-    <t>6785514682</t>
-  </si>
-  <si>
-    <t>00001043</t>
-  </si>
-  <si>
-    <t>3126865548</t>
-  </si>
-  <si>
-    <t>00001044</t>
-  </si>
-  <si>
-    <t>7732207561</t>
-  </si>
-  <si>
-    <t>00001045</t>
-  </si>
-  <si>
-    <t>3128906273</t>
-  </si>
-  <si>
-    <t>00001046</t>
-  </si>
-  <si>
-    <t>7312678849</t>
-  </si>
-  <si>
-    <t>00001047</t>
-  </si>
-  <si>
-    <t>2147787758</t>
-  </si>
-  <si>
-    <t>00001048</t>
-  </si>
-  <si>
-    <t>7087907735</t>
-  </si>
-  <si>
-    <t>00001049</t>
-  </si>
-  <si>
-    <t>18033783691</t>
-  </si>
-  <si>
-    <t>00001050</t>
-  </si>
-  <si>
-    <t>7318030346</t>
-  </si>
-  <si>
-    <t>00001051</t>
-  </si>
-  <si>
-    <t>7739394604</t>
-  </si>
-  <si>
-    <t>00001052</t>
-  </si>
-  <si>
-    <t>4432972742</t>
-  </si>
-  <si>
-    <t>00001053</t>
-  </si>
-  <si>
-    <t>7733798263</t>
-  </si>
-  <si>
-    <t>00001054</t>
-  </si>
-  <si>
-    <t>3464569315</t>
-  </si>
-  <si>
-    <t>00001055</t>
-  </si>
-  <si>
-    <t>5138063642</t>
-  </si>
-  <si>
-    <t>00001056</t>
-  </si>
-  <si>
-    <t>9015816187</t>
-  </si>
-  <si>
-    <t>00001057</t>
-  </si>
-  <si>
-    <t>2192168985</t>
-  </si>
-  <si>
-    <t>00001058</t>
-  </si>
-  <si>
-    <t>3177020168</t>
-  </si>
-  <si>
-    <t>00001059</t>
-  </si>
-  <si>
-    <t>4146307617</t>
+    <t>3059881172</t>
+  </si>
+  <si>
+    <t>08/04/2026 10:27</t>
+  </si>
+  <si>
+    <t>00127349</t>
+  </si>
+  <si>
+    <t>8038629193</t>
+  </si>
+  <si>
+    <t>08/04/2026 10:20</t>
+  </si>
+  <si>
+    <t>00127348</t>
+  </si>
+  <si>
+    <t>5202565961</t>
+  </si>
+  <si>
+    <t>08/04/2026 10:12</t>
+  </si>
+  <si>
+    <t>00127347</t>
+  </si>
+  <si>
+    <t>3372814634</t>
+  </si>
+  <si>
+    <t>08/04/2026 10:10</t>
+  </si>
+  <si>
+    <t>00127346</t>
+  </si>
+  <si>
+    <t>2515098607</t>
+  </si>
+  <si>
+    <t>08/04/2026 09:52</t>
+  </si>
+  <si>
+    <t>00127345</t>
+  </si>
+  <si>
+    <t>Sanyuj Kadam</t>
+  </si>
+  <si>
+    <t>9297987024</t>
+  </si>
+  <si>
+    <t>08/04/2026 09:46</t>
+  </si>
+  <si>
+    <t>00127344</t>
+  </si>
+  <si>
+    <t>2483150263</t>
+  </si>
+  <si>
+    <t>08/04/2026 09:33</t>
+  </si>
+  <si>
+    <t>00127343</t>
+  </si>
+  <si>
+    <t>08/04/2026 09:23</t>
+  </si>
+  <si>
+    <t>00127342</t>
+  </si>
+  <si>
+    <t>Transferred</t>
+  </si>
+  <si>
+    <t>Roblox</t>
+  </si>
+  <si>
+    <t>4697474990</t>
+  </si>
+  <si>
+    <t>08/04/2026 09:14</t>
+  </si>
+  <si>
+    <t>00127341</t>
+  </si>
+  <si>
+    <t>Saba Mulla</t>
+  </si>
+  <si>
+    <t>6128673439</t>
+  </si>
+  <si>
+    <t>08/04/2026 09:12</t>
+  </si>
+  <si>
+    <t>00127340</t>
+  </si>
+  <si>
+    <t>3214058806</t>
+  </si>
+  <si>
+    <t>08/04/2026 04:31</t>
+  </si>
+  <si>
+    <t>00127339</t>
+  </si>
+  <si>
+    <t>5749995236</t>
+  </si>
+  <si>
+    <t>08/04/2026 03:13</t>
   </si>
 </sst>
 </file>
@@ -670,16 +1384,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J31"/>
+  <dimension ref="A1:J89"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="13" customWidth="1"/>
-    <col min="2" max="2" width="8" customWidth="1"/>
-    <col min="3" max="3" width="22" customWidth="1"/>
-    <col min="4" max="4" width="14" customWidth="1"/>
+    <col min="1" max="2" width="13" customWidth="1"/>
+    <col min="3" max="4" width="14" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
-    <col min="7" max="7" width="17" customWidth="1"/>
+    <col min="7" max="7" width="28" customWidth="1"/>
     <col min="8" max="8" width="7" customWidth="1"/>
     <col min="9" max="9" width="13" customWidth="1"/>
     <col min="10" max="10" width="18" customWidth="1"/>
@@ -757,10 +1469,10 @@
         <v>11</v>
       </c>
       <c r="C3" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="D3" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="E3" t="s">
         <v>14</v>
@@ -769,16 +1481,16 @@
         <v>15</v>
       </c>
       <c r="G3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I3" t="s">
         <v>22</v>
       </c>
-      <c r="H3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I3" t="s">
+      <c r="J3" t="s">
         <v>23</v>
-      </c>
-      <c r="J3" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
@@ -786,10 +1498,10 @@
         <v>24</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="C4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D4" t="s">
         <v>13</v>
@@ -801,7 +1513,7 @@
         <v>15</v>
       </c>
       <c r="G4" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="H4" t="s">
         <v>17</v>
@@ -810,18 +1522,18 @@
         <v>27</v>
       </c>
       <c r="J4" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="C5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D5" t="s">
         <v>13</v>
@@ -830,126 +1542,126 @@
         <v>14</v>
       </c>
       <c r="F5" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="G5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H5" t="s">
         <v>17</v>
       </c>
       <c r="I5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J5" t="s">
-        <v>19</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B6" t="s">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="C6" t="s">
-        <v>12</v>
+        <v>37</v>
       </c>
       <c r="D6" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="E6" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="F6" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G6" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H6" t="s">
         <v>17</v>
       </c>
       <c r="I6" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="J6" t="s">
-        <v>19</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="B7" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="C7" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="D7" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="E7" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="F7" t="s">
         <v>15</v>
       </c>
       <c r="G7" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="H7" t="s">
         <v>17</v>
       </c>
       <c r="I7" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="J7" t="s">
-        <v>19</v>
+        <v>46</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="B8" t="s">
         <v>11</v>
       </c>
       <c r="C8" t="s">
-        <v>41</v>
+        <v>12</v>
       </c>
       <c r="D8" t="s">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="E8" t="s">
         <v>14</v>
       </c>
       <c r="F8" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="G8" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="H8" t="s">
         <v>17</v>
       </c>
       <c r="I8" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="J8" t="s">
-        <v>19</v>
+        <v>51</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="B9" t="s">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="C9" t="s">
-        <v>12</v>
+        <v>37</v>
       </c>
       <c r="D9" t="s">
         <v>13</v>
@@ -958,65 +1670,65 @@
         <v>14</v>
       </c>
       <c r="F9" t="s">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="G9" t="s">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="H9" t="s">
         <v>17</v>
       </c>
       <c r="I9" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="J9" t="s">
-        <v>19</v>
+        <v>51</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="B10" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="C10" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="D10" t="s">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="E10" t="s">
         <v>14</v>
       </c>
       <c r="F10" t="s">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="G10" t="s">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="H10" t="s">
         <v>17</v>
       </c>
       <c r="I10" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="J10" t="s">
-        <v>19</v>
+        <v>58</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="B11" t="s">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="C11" t="s">
-        <v>37</v>
+        <v>60</v>
       </c>
       <c r="D11" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="E11" t="s">
         <v>14</v>
@@ -1025,59 +1737,59 @@
         <v>15</v>
       </c>
       <c r="G11" t="s">
-        <v>26</v>
+        <v>61</v>
       </c>
       <c r="H11" t="s">
         <v>17</v>
       </c>
       <c r="I11" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="J11" t="s">
-        <v>19</v>
+        <v>58</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="B12" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="C12" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="D12" t="s">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="E12" t="s">
         <v>14</v>
       </c>
       <c r="F12" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G12" t="s">
-        <v>34</v>
+        <v>64</v>
       </c>
       <c r="H12" t="s">
         <v>17</v>
       </c>
       <c r="I12" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="J12" t="s">
-        <v>19</v>
+        <v>66</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="B13" t="s">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="C13" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="D13" t="s">
         <v>13</v>
@@ -1086,62 +1798,62 @@
         <v>14</v>
       </c>
       <c r="F13" t="s">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="G13" t="s">
-        <v>16</v>
+        <v>68</v>
       </c>
       <c r="H13" t="s">
         <v>17</v>
       </c>
       <c r="I13" t="s">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="J13" t="s">
-        <v>19</v>
+        <v>70</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>54</v>
+        <v>71</v>
       </c>
       <c r="B14" t="s">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="C14" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="D14" t="s">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="E14" t="s">
         <v>14</v>
       </c>
       <c r="F14" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="G14" t="s">
-        <v>34</v>
+        <v>72</v>
       </c>
       <c r="H14" t="s">
         <v>17</v>
       </c>
       <c r="I14" t="s">
-        <v>56</v>
+        <v>73</v>
       </c>
       <c r="J14" t="s">
-        <v>19</v>
+        <v>74</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="B15" t="s">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="C15" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="D15" t="s">
         <v>13</v>
@@ -1153,59 +1865,59 @@
         <v>15</v>
       </c>
       <c r="G15" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="H15" t="s">
         <v>17</v>
       </c>
       <c r="I15" t="s">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="J15" t="s">
-        <v>19</v>
+        <v>74</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="B16" t="s">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="C16" t="s">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="D16" t="s">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="E16" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="F16" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G16" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="H16" t="s">
         <v>17</v>
       </c>
       <c r="I16" t="s">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="J16" t="s">
-        <v>19</v>
+        <v>74</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="B17" t="s">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="C17" t="s">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="D17" t="s">
         <v>13</v>
@@ -1217,123 +1929,123 @@
         <v>15</v>
       </c>
       <c r="G17" t="s">
-        <v>38</v>
+        <v>80</v>
       </c>
       <c r="H17" t="s">
         <v>17</v>
       </c>
       <c r="I17" t="s">
-        <v>62</v>
+        <v>81</v>
       </c>
       <c r="J17" t="s">
-        <v>19</v>
+        <v>82</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>63</v>
+        <v>83</v>
       </c>
       <c r="B18" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="C18" t="s">
-        <v>41</v>
+        <v>84</v>
       </c>
       <c r="D18" t="s">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="E18" t="s">
         <v>14</v>
       </c>
       <c r="F18" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G18" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="H18" t="s">
         <v>17</v>
       </c>
       <c r="I18" t="s">
-        <v>64</v>
+        <v>85</v>
       </c>
       <c r="J18" t="s">
-        <v>19</v>
+        <v>86</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>65</v>
+        <v>87</v>
       </c>
       <c r="B19" t="s">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="C19" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="D19" t="s">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="E19" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="F19" t="s">
-        <v>17</v>
+        <v>88</v>
       </c>
       <c r="G19" t="s">
-        <v>34</v>
+        <v>89</v>
       </c>
       <c r="H19" t="s">
         <v>17</v>
       </c>
       <c r="I19" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="J19" t="s">
-        <v>19</v>
+        <v>91</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>67</v>
+        <v>92</v>
       </c>
       <c r="B20" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="C20" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D20" t="s">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="E20" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="F20" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G20" t="s">
-        <v>34</v>
+        <v>93</v>
       </c>
       <c r="H20" t="s">
         <v>17</v>
       </c>
       <c r="I20" t="s">
-        <v>68</v>
+        <v>94</v>
       </c>
       <c r="J20" t="s">
-        <v>19</v>
+        <v>95</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>69</v>
+        <v>96</v>
       </c>
       <c r="B21" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="C21" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="D21" t="s">
         <v>13</v>
@@ -1342,65 +2054,65 @@
         <v>14</v>
       </c>
       <c r="F21" t="s">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="G21" t="s">
-        <v>38</v>
+        <v>97</v>
       </c>
       <c r="H21" t="s">
         <v>17</v>
       </c>
       <c r="I21" t="s">
-        <v>70</v>
+        <v>98</v>
       </c>
       <c r="J21" t="s">
-        <v>19</v>
+        <v>99</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>71</v>
+        <v>100</v>
       </c>
       <c r="B22" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="C22" t="s">
-        <v>55</v>
+        <v>84</v>
       </c>
       <c r="D22" t="s">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="E22" t="s">
         <v>14</v>
       </c>
       <c r="F22" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="G22" t="s">
-        <v>34</v>
+        <v>101</v>
       </c>
       <c r="H22" t="s">
         <v>17</v>
       </c>
       <c r="I22" t="s">
-        <v>72</v>
+        <v>102</v>
       </c>
       <c r="J22" t="s">
-        <v>19</v>
+        <v>103</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="B23" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="C23" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="D23" t="s">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="E23" t="s">
         <v>14</v>
@@ -1409,222 +2121,222 @@
         <v>15</v>
       </c>
       <c r="G23" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="H23" t="s">
         <v>17</v>
       </c>
       <c r="I23" t="s">
-        <v>74</v>
+        <v>105</v>
       </c>
       <c r="J23" t="s">
-        <v>19</v>
+        <v>106</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>75</v>
+        <v>107</v>
       </c>
       <c r="B24" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="C24" t="s">
-        <v>37</v>
+        <v>84</v>
       </c>
       <c r="D24" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="E24" t="s">
         <v>14</v>
       </c>
       <c r="F24" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G24" t="s">
-        <v>34</v>
+        <v>80</v>
       </c>
       <c r="H24" t="s">
         <v>17</v>
       </c>
       <c r="I24" t="s">
-        <v>76</v>
+        <v>108</v>
       </c>
       <c r="J24" t="s">
-        <v>19</v>
+        <v>109</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>77</v>
+        <v>110</v>
       </c>
       <c r="B25" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="C25" t="s">
-        <v>41</v>
+        <v>84</v>
       </c>
       <c r="D25" t="s">
-        <v>42</v>
+        <v>111</v>
       </c>
       <c r="E25" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="F25" t="s">
-        <v>17</v>
+        <v>88</v>
       </c>
       <c r="G25" t="s">
-        <v>34</v>
+        <v>89</v>
       </c>
       <c r="H25" t="s">
         <v>17</v>
       </c>
       <c r="I25" t="s">
-        <v>78</v>
+        <v>112</v>
       </c>
       <c r="J25" t="s">
-        <v>19</v>
+        <v>113</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>79</v>
+        <v>114</v>
       </c>
       <c r="B26" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="C26" t="s">
-        <v>12</v>
+        <v>84</v>
       </c>
       <c r="D26" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="E26" t="s">
         <v>14</v>
       </c>
       <c r="F26" t="s">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="G26" t="s">
-        <v>16</v>
+        <v>115</v>
       </c>
       <c r="H26" t="s">
         <v>17</v>
       </c>
       <c r="I26" t="s">
-        <v>80</v>
+        <v>116</v>
       </c>
       <c r="J26" t="s">
-        <v>19</v>
+        <v>117</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>81</v>
+        <v>118</v>
       </c>
       <c r="B27" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="C27" t="s">
-        <v>12</v>
+        <v>84</v>
       </c>
       <c r="D27" t="s">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="E27" t="s">
         <v>14</v>
       </c>
       <c r="F27" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="G27" t="s">
-        <v>34</v>
+        <v>119</v>
       </c>
       <c r="H27" t="s">
         <v>17</v>
       </c>
       <c r="I27" t="s">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="J27" t="s">
-        <v>19</v>
+        <v>121</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>83</v>
+        <v>122</v>
       </c>
       <c r="B28" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="C28" t="s">
-        <v>41</v>
+        <v>84</v>
       </c>
       <c r="D28" t="s">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="E28" t="s">
         <v>14</v>
       </c>
       <c r="F28" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="G28" t="s">
-        <v>34</v>
+        <v>72</v>
       </c>
       <c r="H28" t="s">
         <v>17</v>
       </c>
       <c r="I28" t="s">
-        <v>84</v>
+        <v>123</v>
       </c>
       <c r="J28" t="s">
-        <v>19</v>
+        <v>124</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>85</v>
+        <v>125</v>
       </c>
       <c r="B29" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="C29" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="D29" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="E29" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="F29" t="s">
-        <v>17</v>
+        <v>88</v>
       </c>
       <c r="G29" t="s">
-        <v>34</v>
+        <v>89</v>
       </c>
       <c r="H29" t="s">
         <v>17</v>
       </c>
       <c r="I29" t="s">
-        <v>86</v>
+        <v>126</v>
       </c>
       <c r="J29" t="s">
-        <v>19</v>
+        <v>127</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>87</v>
+        <v>128</v>
       </c>
       <c r="B30" t="s">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="C30" t="s">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="D30" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="E30" t="s">
         <v>14</v>
@@ -1633,48 +2345,1904 @@
         <v>15</v>
       </c>
       <c r="G30" t="s">
-        <v>22</v>
+        <v>64</v>
       </c>
       <c r="H30" t="s">
         <v>17</v>
       </c>
       <c r="I30" t="s">
-        <v>88</v>
+        <v>129</v>
       </c>
       <c r="J30" t="s">
-        <v>19</v>
+        <v>127</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
+        <v>130</v>
+      </c>
+      <c r="B31" t="s">
+        <v>30</v>
+      </c>
+      <c r="C31" t="s">
+        <v>43</v>
+      </c>
+      <c r="D31" t="s">
+        <v>13</v>
+      </c>
+      <c r="E31" t="s">
+        <v>14</v>
+      </c>
+      <c r="F31" t="s">
+        <v>48</v>
+      </c>
+      <c r="G31" t="s">
+        <v>131</v>
+      </c>
+      <c r="H31" t="s">
+        <v>17</v>
+      </c>
+      <c r="I31" t="s">
+        <v>132</v>
+      </c>
+      <c r="J31" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>134</v>
+      </c>
+      <c r="B32" t="s">
+        <v>36</v>
+      </c>
+      <c r="C32" t="s">
+        <v>60</v>
+      </c>
+      <c r="D32" t="s">
+        <v>13</v>
+      </c>
+      <c r="E32" t="s">
+        <v>14</v>
+      </c>
+      <c r="F32" t="s">
+        <v>15</v>
+      </c>
+      <c r="G32" t="s">
+        <v>135</v>
+      </c>
+      <c r="H32" t="s">
+        <v>17</v>
+      </c>
+      <c r="I32" t="s">
+        <v>136</v>
+      </c>
+      <c r="J32" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>138</v>
+      </c>
+      <c r="B33" t="s">
+        <v>25</v>
+      </c>
+      <c r="C33" t="s">
+        <v>26</v>
+      </c>
+      <c r="D33" t="s">
+        <v>13</v>
+      </c>
+      <c r="E33" t="s">
+        <v>38</v>
+      </c>
+      <c r="F33" t="s">
+        <v>15</v>
+      </c>
+      <c r="G33" t="s">
+        <v>39</v>
+      </c>
+      <c r="H33" t="s">
+        <v>17</v>
+      </c>
+      <c r="I33" t="s">
+        <v>139</v>
+      </c>
+      <c r="J33" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>141</v>
+      </c>
+      <c r="B34" t="s">
+        <v>30</v>
+      </c>
+      <c r="C34" t="s">
+        <v>84</v>
+      </c>
+      <c r="D34" t="s">
+        <v>13</v>
+      </c>
+      <c r="E34" t="s">
+        <v>142</v>
+      </c>
+      <c r="F34" t="s">
+        <v>88</v>
+      </c>
+      <c r="G34" t="s">
+        <v>143</v>
+      </c>
+      <c r="H34" t="s">
+        <v>17</v>
+      </c>
+      <c r="I34" t="s">
+        <v>144</v>
+      </c>
+      <c r="J34" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>146</v>
+      </c>
+      <c r="B35" t="s">
+        <v>30</v>
+      </c>
+      <c r="C35" t="s">
+        <v>31</v>
+      </c>
+      <c r="D35" t="s">
+        <v>13</v>
+      </c>
+      <c r="E35" t="s">
+        <v>38</v>
+      </c>
+      <c r="F35" t="s">
+        <v>88</v>
+      </c>
+      <c r="G35" t="s">
         <v>89</v>
       </c>
-      <c r="B31" t="s">
+      <c r="H35" t="s">
+        <v>17</v>
+      </c>
+      <c r="I35" t="s">
+        <v>147</v>
+      </c>
+      <c r="J35" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>148</v>
+      </c>
+      <c r="B36" t="s">
+        <v>30</v>
+      </c>
+      <c r="C36" t="s">
+        <v>84</v>
+      </c>
+      <c r="D36" t="s">
+        <v>13</v>
+      </c>
+      <c r="E36" t="s">
+        <v>14</v>
+      </c>
+      <c r="F36" t="s">
+        <v>15</v>
+      </c>
+      <c r="G36" t="s">
+        <v>32</v>
+      </c>
+      <c r="H36" t="s">
+        <v>17</v>
+      </c>
+      <c r="I36" t="s">
+        <v>149</v>
+      </c>
+      <c r="J36" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>151</v>
+      </c>
+      <c r="B37" t="s">
+        <v>30</v>
+      </c>
+      <c r="C37" t="s">
+        <v>31</v>
+      </c>
+      <c r="D37" t="s">
+        <v>13</v>
+      </c>
+      <c r="E37" t="s">
+        <v>14</v>
+      </c>
+      <c r="F37" t="s">
+        <v>15</v>
+      </c>
+      <c r="G37" t="s">
+        <v>44</v>
+      </c>
+      <c r="H37" t="s">
+        <v>17</v>
+      </c>
+      <c r="I37" t="s">
+        <v>152</v>
+      </c>
+      <c r="J37" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>153</v>
+      </c>
+      <c r="B38" t="s">
+        <v>36</v>
+      </c>
+      <c r="C38" t="s">
+        <v>60</v>
+      </c>
+      <c r="D38" t="s">
+        <v>13</v>
+      </c>
+      <c r="E38" t="s">
+        <v>38</v>
+      </c>
+      <c r="F38" t="s">
+        <v>17</v>
+      </c>
+      <c r="G38" t="s">
+        <v>154</v>
+      </c>
+      <c r="H38" t="s">
+        <v>17</v>
+      </c>
+      <c r="I38" t="s">
+        <v>155</v>
+      </c>
+      <c r="J38" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>157</v>
+      </c>
+      <c r="B39" t="s">
+        <v>30</v>
+      </c>
+      <c r="C39" t="s">
+        <v>31</v>
+      </c>
+      <c r="D39" t="s">
+        <v>13</v>
+      </c>
+      <c r="E39" t="s">
+        <v>14</v>
+      </c>
+      <c r="F39" t="s">
+        <v>15</v>
+      </c>
+      <c r="G39" t="s">
+        <v>44</v>
+      </c>
+      <c r="H39" t="s">
+        <v>17</v>
+      </c>
+      <c r="I39" t="s">
+        <v>158</v>
+      </c>
+      <c r="J39" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>160</v>
+      </c>
+      <c r="B40" t="s">
+        <v>36</v>
+      </c>
+      <c r="C40" t="s">
+        <v>60</v>
+      </c>
+      <c r="D40" t="s">
+        <v>13</v>
+      </c>
+      <c r="E40" t="s">
+        <v>38</v>
+      </c>
+      <c r="F40" t="s">
+        <v>15</v>
+      </c>
+      <c r="G40" t="s">
+        <v>39</v>
+      </c>
+      <c r="H40" t="s">
+        <v>17</v>
+      </c>
+      <c r="I40" t="s">
+        <v>161</v>
+      </c>
+      <c r="J40" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>163</v>
+      </c>
+      <c r="B41" t="s">
+        <v>30</v>
+      </c>
+      <c r="C41" t="s">
+        <v>84</v>
+      </c>
+      <c r="D41" t="s">
+        <v>13</v>
+      </c>
+      <c r="E41" t="s">
+        <v>14</v>
+      </c>
+      <c r="F41" t="s">
+        <v>15</v>
+      </c>
+      <c r="G41" t="s">
+        <v>164</v>
+      </c>
+      <c r="H41" t="s">
+        <v>17</v>
+      </c>
+      <c r="I41" t="s">
+        <v>165</v>
+      </c>
+      <c r="J41" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>167</v>
+      </c>
+      <c r="B42" t="s">
+        <v>30</v>
+      </c>
+      <c r="C42" t="s">
+        <v>31</v>
+      </c>
+      <c r="D42" t="s">
+        <v>13</v>
+      </c>
+      <c r="E42" t="s">
+        <v>14</v>
+      </c>
+      <c r="F42" t="s">
+        <v>15</v>
+      </c>
+      <c r="G42" t="s">
+        <v>168</v>
+      </c>
+      <c r="H42" t="s">
+        <v>17</v>
+      </c>
+      <c r="I42" t="s">
+        <v>169</v>
+      </c>
+      <c r="J42" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>171</v>
+      </c>
+      <c r="B43" t="s">
+        <v>30</v>
+      </c>
+      <c r="C43" t="s">
+        <v>172</v>
+      </c>
+      <c r="D43" t="s">
+        <v>13</v>
+      </c>
+      <c r="E43" t="s">
+        <v>14</v>
+      </c>
+      <c r="F43" t="s">
+        <v>15</v>
+      </c>
+      <c r="G43" t="s">
+        <v>80</v>
+      </c>
+      <c r="H43" t="s">
+        <v>17</v>
+      </c>
+      <c r="I43" t="s">
+        <v>173</v>
+      </c>
+      <c r="J43" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>175</v>
+      </c>
+      <c r="B44" t="s">
+        <v>36</v>
+      </c>
+      <c r="C44" t="s">
+        <v>176</v>
+      </c>
+      <c r="D44" t="s">
+        <v>13</v>
+      </c>
+      <c r="E44" t="s">
+        <v>14</v>
+      </c>
+      <c r="F44" t="s">
+        <v>48</v>
+      </c>
+      <c r="G44" t="s">
+        <v>131</v>
+      </c>
+      <c r="H44" t="s">
+        <v>17</v>
+      </c>
+      <c r="I44" t="s">
+        <v>177</v>
+      </c>
+      <c r="J44" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>179</v>
+      </c>
+      <c r="B45" t="s">
+        <v>25</v>
+      </c>
+      <c r="C45" t="s">
+        <v>26</v>
+      </c>
+      <c r="D45" t="s">
+        <v>13</v>
+      </c>
+      <c r="E45" t="s">
+        <v>14</v>
+      </c>
+      <c r="F45" t="s">
+        <v>15</v>
+      </c>
+      <c r="G45" t="s">
+        <v>64</v>
+      </c>
+      <c r="H45" t="s">
+        <v>17</v>
+      </c>
+      <c r="I45" t="s">
+        <v>180</v>
+      </c>
+      <c r="J45" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>182</v>
+      </c>
+      <c r="B46" t="s">
+        <v>36</v>
+      </c>
+      <c r="C46" t="s">
+        <v>37</v>
+      </c>
+      <c r="D46" t="s">
+        <v>13</v>
+      </c>
+      <c r="E46" t="s">
+        <v>14</v>
+      </c>
+      <c r="F46" t="s">
+        <v>48</v>
+      </c>
+      <c r="G46" t="s">
+        <v>72</v>
+      </c>
+      <c r="H46" t="s">
+        <v>17</v>
+      </c>
+      <c r="I46" t="s">
+        <v>183</v>
+      </c>
+      <c r="J46" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>185</v>
+      </c>
+      <c r="B47" t="s">
+        <v>36</v>
+      </c>
+      <c r="C47" t="s">
+        <v>60</v>
+      </c>
+      <c r="D47" t="s">
+        <v>13</v>
+      </c>
+      <c r="E47" t="s">
+        <v>38</v>
+      </c>
+      <c r="F47" t="s">
+        <v>15</v>
+      </c>
+      <c r="G47" t="s">
+        <v>39</v>
+      </c>
+      <c r="H47" t="s">
+        <v>17</v>
+      </c>
+      <c r="I47" t="s">
+        <v>186</v>
+      </c>
+      <c r="J47" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>188</v>
+      </c>
+      <c r="B48" t="s">
+        <v>36</v>
+      </c>
+      <c r="C48" t="s">
+        <v>37</v>
+      </c>
+      <c r="D48" t="s">
+        <v>13</v>
+      </c>
+      <c r="E48" t="s">
+        <v>38</v>
+      </c>
+      <c r="F48" t="s">
+        <v>15</v>
+      </c>
+      <c r="G48" t="s">
+        <v>44</v>
+      </c>
+      <c r="H48" t="s">
+        <v>17</v>
+      </c>
+      <c r="I48" t="s">
+        <v>189</v>
+      </c>
+      <c r="J48" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>191</v>
+      </c>
+      <c r="B49" t="s">
+        <v>25</v>
+      </c>
+      <c r="C49" t="s">
+        <v>26</v>
+      </c>
+      <c r="D49" t="s">
+        <v>13</v>
+      </c>
+      <c r="E49" t="s">
+        <v>38</v>
+      </c>
+      <c r="F49" t="s">
+        <v>15</v>
+      </c>
+      <c r="G49" t="s">
+        <v>192</v>
+      </c>
+      <c r="H49" t="s">
+        <v>17</v>
+      </c>
+      <c r="I49" t="s">
+        <v>193</v>
+      </c>
+      <c r="J49" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>195</v>
+      </c>
+      <c r="B50" t="s">
+        <v>36</v>
+      </c>
+      <c r="C50" t="s">
+        <v>37</v>
+      </c>
+      <c r="D50" t="s">
+        <v>13</v>
+      </c>
+      <c r="E50" t="s">
+        <v>14</v>
+      </c>
+      <c r="F50" t="s">
+        <v>48</v>
+      </c>
+      <c r="G50" t="s">
+        <v>196</v>
+      </c>
+      <c r="H50" t="s">
+        <v>17</v>
+      </c>
+      <c r="I50" t="s">
+        <v>197</v>
+      </c>
+      <c r="J50" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>199</v>
+      </c>
+      <c r="B51" t="s">
+        <v>36</v>
+      </c>
+      <c r="C51" t="s">
+        <v>200</v>
+      </c>
+      <c r="D51" t="s">
+        <v>13</v>
+      </c>
+      <c r="E51" t="s">
+        <v>38</v>
+      </c>
+      <c r="F51" t="s">
+        <v>88</v>
+      </c>
+      <c r="G51" t="s">
+        <v>143</v>
+      </c>
+      <c r="H51" t="s">
+        <v>17</v>
+      </c>
+      <c r="I51" t="s">
+        <v>201</v>
+      </c>
+      <c r="J51" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>203</v>
+      </c>
+      <c r="B52" t="s">
+        <v>30</v>
+      </c>
+      <c r="C52" t="s">
+        <v>31</v>
+      </c>
+      <c r="D52" t="s">
+        <v>13</v>
+      </c>
+      <c r="E52" t="s">
+        <v>14</v>
+      </c>
+      <c r="F52" t="s">
+        <v>48</v>
+      </c>
+      <c r="G52" t="s">
+        <v>204</v>
+      </c>
+      <c r="H52" t="s">
+        <v>17</v>
+      </c>
+      <c r="I52" t="s">
+        <v>205</v>
+      </c>
+      <c r="J52" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>207</v>
+      </c>
+      <c r="B53" t="s">
+        <v>30</v>
+      </c>
+      <c r="C53" t="s">
+        <v>31</v>
+      </c>
+      <c r="D53" t="s">
+        <v>13</v>
+      </c>
+      <c r="E53" t="s">
+        <v>14</v>
+      </c>
+      <c r="F53" t="s">
+        <v>48</v>
+      </c>
+      <c r="G53" t="s">
+        <v>208</v>
+      </c>
+      <c r="H53" t="s">
+        <v>17</v>
+      </c>
+      <c r="I53" t="s">
+        <v>209</v>
+      </c>
+      <c r="J53" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>211</v>
+      </c>
+      <c r="B54" t="s">
+        <v>36</v>
+      </c>
+      <c r="C54" t="s">
+        <v>60</v>
+      </c>
+      <c r="D54" t="s">
+        <v>13</v>
+      </c>
+      <c r="E54" t="s">
+        <v>14</v>
+      </c>
+      <c r="F54" t="s">
+        <v>15</v>
+      </c>
+      <c r="G54" t="s">
+        <v>16</v>
+      </c>
+      <c r="H54" t="s">
+        <v>17</v>
+      </c>
+      <c r="I54" t="s">
+        <v>212</v>
+      </c>
+      <c r="J54" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>214</v>
+      </c>
+      <c r="B55" t="s">
+        <v>30</v>
+      </c>
+      <c r="C55" t="s">
+        <v>172</v>
+      </c>
+      <c r="D55" t="s">
+        <v>13</v>
+      </c>
+      <c r="E55" t="s">
+        <v>14</v>
+      </c>
+      <c r="F55" t="s">
+        <v>48</v>
+      </c>
+      <c r="G55" t="s">
+        <v>72</v>
+      </c>
+      <c r="H55" t="s">
+        <v>17</v>
+      </c>
+      <c r="I55" t="s">
+        <v>215</v>
+      </c>
+      <c r="J55" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>217</v>
+      </c>
+      <c r="B56" t="s">
+        <v>25</v>
+      </c>
+      <c r="C56" t="s">
+        <v>26</v>
+      </c>
+      <c r="D56" t="s">
+        <v>13</v>
+      </c>
+      <c r="E56" t="s">
+        <v>14</v>
+      </c>
+      <c r="F56" t="s">
+        <v>48</v>
+      </c>
+      <c r="G56" t="s">
+        <v>218</v>
+      </c>
+      <c r="H56" t="s">
+        <v>17</v>
+      </c>
+      <c r="I56" t="s">
+        <v>219</v>
+      </c>
+      <c r="J56" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>221</v>
+      </c>
+      <c r="B57" t="s">
+        <v>36</v>
+      </c>
+      <c r="C57" t="s">
+        <v>37</v>
+      </c>
+      <c r="D57" t="s">
+        <v>13</v>
+      </c>
+      <c r="E57" t="s">
+        <v>14</v>
+      </c>
+      <c r="F57" t="s">
+        <v>48</v>
+      </c>
+      <c r="G57" t="s">
+        <v>218</v>
+      </c>
+      <c r="H57" t="s">
+        <v>17</v>
+      </c>
+      <c r="I57" t="s">
+        <v>222</v>
+      </c>
+      <c r="J57" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>224</v>
+      </c>
+      <c r="B58" t="s">
+        <v>30</v>
+      </c>
+      <c r="C58" t="s">
+        <v>43</v>
+      </c>
+      <c r="D58" t="s">
+        <v>13</v>
+      </c>
+      <c r="E58" t="s">
+        <v>14</v>
+      </c>
+      <c r="F58" t="s">
+        <v>15</v>
+      </c>
+      <c r="G58" t="s">
+        <v>16</v>
+      </c>
+      <c r="H58" t="s">
+        <v>17</v>
+      </c>
+      <c r="I58" t="s">
+        <v>225</v>
+      </c>
+      <c r="J58" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>227</v>
+      </c>
+      <c r="B59" t="s">
+        <v>25</v>
+      </c>
+      <c r="C59" t="s">
+        <v>26</v>
+      </c>
+      <c r="D59" t="s">
+        <v>13</v>
+      </c>
+      <c r="E59" t="s">
+        <v>14</v>
+      </c>
+      <c r="F59" t="s">
+        <v>48</v>
+      </c>
+      <c r="G59" t="s">
+        <v>228</v>
+      </c>
+      <c r="H59" t="s">
+        <v>17</v>
+      </c>
+      <c r="I59" t="s">
+        <v>229</v>
+      </c>
+      <c r="J59" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>231</v>
+      </c>
+      <c r="B60" t="s">
+        <v>36</v>
+      </c>
+      <c r="C60" t="s">
+        <v>60</v>
+      </c>
+      <c r="D60" t="s">
+        <v>13</v>
+      </c>
+      <c r="E60" t="s">
+        <v>14</v>
+      </c>
+      <c r="F60" t="s">
+        <v>48</v>
+      </c>
+      <c r="G60" t="s">
+        <v>196</v>
+      </c>
+      <c r="H60" t="s">
+        <v>17</v>
+      </c>
+      <c r="I60" t="s">
+        <v>232</v>
+      </c>
+      <c r="J60" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>234</v>
+      </c>
+      <c r="B61" t="s">
+        <v>25</v>
+      </c>
+      <c r="C61" t="s">
+        <v>26</v>
+      </c>
+      <c r="D61" t="s">
+        <v>13</v>
+      </c>
+      <c r="E61" t="s">
+        <v>38</v>
+      </c>
+      <c r="F61" t="s">
+        <v>15</v>
+      </c>
+      <c r="G61" t="s">
+        <v>44</v>
+      </c>
+      <c r="H61" t="s">
+        <v>17</v>
+      </c>
+      <c r="I61" t="s">
+        <v>235</v>
+      </c>
+      <c r="J61" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>237</v>
+      </c>
+      <c r="B62" t="s">
+        <v>30</v>
+      </c>
+      <c r="C62" t="s">
+        <v>31</v>
+      </c>
+      <c r="D62" t="s">
+        <v>13</v>
+      </c>
+      <c r="E62" t="s">
+        <v>14</v>
+      </c>
+      <c r="F62" t="s">
+        <v>48</v>
+      </c>
+      <c r="G62" t="s">
+        <v>101</v>
+      </c>
+      <c r="H62" t="s">
+        <v>17</v>
+      </c>
+      <c r="I62" t="s">
+        <v>238</v>
+      </c>
+      <c r="J62" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>240</v>
+      </c>
+      <c r="B63" t="s">
+        <v>30</v>
+      </c>
+      <c r="C63" t="s">
+        <v>84</v>
+      </c>
+      <c r="D63" t="s">
+        <v>13</v>
+      </c>
+      <c r="E63" t="s">
+        <v>38</v>
+      </c>
+      <c r="F63" t="s">
+        <v>15</v>
+      </c>
+      <c r="G63" t="s">
+        <v>44</v>
+      </c>
+      <c r="H63" t="s">
+        <v>17</v>
+      </c>
+      <c r="I63" t="s">
+        <v>241</v>
+      </c>
+      <c r="J63" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>243</v>
+      </c>
+      <c r="B64" t="s">
+        <v>30</v>
+      </c>
+      <c r="C64" t="s">
+        <v>31</v>
+      </c>
+      <c r="D64" t="s">
+        <v>13</v>
+      </c>
+      <c r="E64" t="s">
+        <v>14</v>
+      </c>
+      <c r="F64" t="s">
+        <v>15</v>
+      </c>
+      <c r="G64" t="s">
+        <v>64</v>
+      </c>
+      <c r="H64" t="s">
+        <v>17</v>
+      </c>
+      <c r="I64" t="s">
+        <v>244</v>
+      </c>
+      <c r="J64" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>246</v>
+      </c>
+      <c r="B65" t="s">
+        <v>25</v>
+      </c>
+      <c r="C65" t="s">
+        <v>26</v>
+      </c>
+      <c r="D65" t="s">
+        <v>13</v>
+      </c>
+      <c r="E65" t="s">
+        <v>14</v>
+      </c>
+      <c r="F65" t="s">
+        <v>15</v>
+      </c>
+      <c r="G65" t="s">
+        <v>64</v>
+      </c>
+      <c r="H65" t="s">
+        <v>17</v>
+      </c>
+      <c r="I65" t="s">
+        <v>247</v>
+      </c>
+      <c r="J65" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>249</v>
+      </c>
+      <c r="B66" t="s">
+        <v>30</v>
+      </c>
+      <c r="C66" t="s">
+        <v>43</v>
+      </c>
+      <c r="D66" t="s">
+        <v>13</v>
+      </c>
+      <c r="E66" t="s">
+        <v>14</v>
+      </c>
+      <c r="F66" t="s">
+        <v>48</v>
+      </c>
+      <c r="G66" t="s">
+        <v>115</v>
+      </c>
+      <c r="H66" t="s">
+        <v>17</v>
+      </c>
+      <c r="I66" t="s">
+        <v>250</v>
+      </c>
+      <c r="J66" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>252</v>
+      </c>
+      <c r="B67" t="s">
+        <v>30</v>
+      </c>
+      <c r="C67" t="s">
+        <v>172</v>
+      </c>
+      <c r="D67" t="s">
+        <v>13</v>
+      </c>
+      <c r="E67" t="s">
+        <v>38</v>
+      </c>
+      <c r="F67" t="s">
+        <v>15</v>
+      </c>
+      <c r="G67" t="s">
+        <v>93</v>
+      </c>
+      <c r="H67" t="s">
+        <v>17</v>
+      </c>
+      <c r="I67" t="s">
+        <v>253</v>
+      </c>
+      <c r="J67" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>255</v>
+      </c>
+      <c r="B68" t="s">
+        <v>30</v>
+      </c>
+      <c r="C68" t="s">
+        <v>31</v>
+      </c>
+      <c r="D68" t="s">
+        <v>13</v>
+      </c>
+      <c r="E68" t="s">
+        <v>14</v>
+      </c>
+      <c r="F68" t="s">
+        <v>15</v>
+      </c>
+      <c r="G68" t="s">
+        <v>256</v>
+      </c>
+      <c r="H68" t="s">
+        <v>17</v>
+      </c>
+      <c r="I68" t="s">
+        <v>257</v>
+      </c>
+      <c r="J68" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>259</v>
+      </c>
+      <c r="B69" t="s">
+        <v>36</v>
+      </c>
+      <c r="C69" t="s">
+        <v>37</v>
+      </c>
+      <c r="D69" t="s">
+        <v>13</v>
+      </c>
+      <c r="E69" t="s">
+        <v>14</v>
+      </c>
+      <c r="F69" t="s">
+        <v>48</v>
+      </c>
+      <c r="G69" t="s">
+        <v>196</v>
+      </c>
+      <c r="H69" t="s">
+        <v>17</v>
+      </c>
+      <c r="I69" t="s">
+        <v>260</v>
+      </c>
+      <c r="J69" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>262</v>
+      </c>
+      <c r="B70" t="s">
+        <v>36</v>
+      </c>
+      <c r="C70" t="s">
+        <v>60</v>
+      </c>
+      <c r="D70" t="s">
+        <v>13</v>
+      </c>
+      <c r="E70" t="s">
+        <v>14</v>
+      </c>
+      <c r="F70" t="s">
+        <v>48</v>
+      </c>
+      <c r="G70" t="s">
+        <v>218</v>
+      </c>
+      <c r="H70" t="s">
+        <v>17</v>
+      </c>
+      <c r="I70" t="s">
+        <v>263</v>
+      </c>
+      <c r="J70" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>265</v>
+      </c>
+      <c r="B71" t="s">
+        <v>30</v>
+      </c>
+      <c r="C71" t="s">
+        <v>266</v>
+      </c>
+      <c r="D71" t="s">
+        <v>13</v>
+      </c>
+      <c r="E71" t="s">
+        <v>14</v>
+      </c>
+      <c r="F71" t="s">
+        <v>15</v>
+      </c>
+      <c r="G71" t="s">
+        <v>64</v>
+      </c>
+      <c r="H71" t="s">
+        <v>17</v>
+      </c>
+      <c r="I71" t="s">
+        <v>267</v>
+      </c>
+      <c r="J71" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>269</v>
+      </c>
+      <c r="B72" t="s">
         <v>11</v>
       </c>
-      <c r="C31" t="s">
-        <v>41</v>
-      </c>
-      <c r="D31" t="s">
-        <v>42</v>
-      </c>
-      <c r="E31" t="s">
-        <v>14</v>
-      </c>
-      <c r="F31" t="s">
-        <v>17</v>
-      </c>
-      <c r="G31" t="s">
-        <v>34</v>
-      </c>
-      <c r="H31" t="s">
-        <v>17</v>
-      </c>
-      <c r="I31" t="s">
-        <v>90</v>
-      </c>
-      <c r="J31" t="s">
-        <v>19</v>
+      <c r="C72" t="s">
+        <v>21</v>
+      </c>
+      <c r="D72" t="s">
+        <v>13</v>
+      </c>
+      <c r="E72" t="s">
+        <v>14</v>
+      </c>
+      <c r="F72" t="s">
+        <v>88</v>
+      </c>
+      <c r="G72" t="s">
+        <v>270</v>
+      </c>
+      <c r="H72" t="s">
+        <v>17</v>
+      </c>
+      <c r="I72" t="s">
+        <v>271</v>
+      </c>
+      <c r="J72" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>273</v>
+      </c>
+      <c r="B73" t="s">
+        <v>30</v>
+      </c>
+      <c r="C73" t="s">
+        <v>43</v>
+      </c>
+      <c r="D73" t="s">
+        <v>13</v>
+      </c>
+      <c r="E73" t="s">
+        <v>14</v>
+      </c>
+      <c r="F73" t="s">
+        <v>48</v>
+      </c>
+      <c r="G73" t="s">
+        <v>72</v>
+      </c>
+      <c r="H73" t="s">
+        <v>17</v>
+      </c>
+      <c r="I73" t="s">
+        <v>274</v>
+      </c>
+      <c r="J73" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>276</v>
+      </c>
+      <c r="B74" t="s">
+        <v>30</v>
+      </c>
+      <c r="C74" t="s">
+        <v>31</v>
+      </c>
+      <c r="D74" t="s">
+        <v>13</v>
+      </c>
+      <c r="E74" t="s">
+        <v>14</v>
+      </c>
+      <c r="F74" t="s">
+        <v>48</v>
+      </c>
+      <c r="G74" t="s">
+        <v>204</v>
+      </c>
+      <c r="H74" t="s">
+        <v>17</v>
+      </c>
+      <c r="I74" t="s">
+        <v>277</v>
+      </c>
+      <c r="J74" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>279</v>
+      </c>
+      <c r="B75" t="s">
+        <v>25</v>
+      </c>
+      <c r="C75" t="s">
+        <v>26</v>
+      </c>
+      <c r="D75" t="s">
+        <v>13</v>
+      </c>
+      <c r="E75" t="s">
+        <v>38</v>
+      </c>
+      <c r="F75" t="s">
+        <v>88</v>
+      </c>
+      <c r="G75" t="s">
+        <v>89</v>
+      </c>
+      <c r="H75" t="s">
+        <v>17</v>
+      </c>
+      <c r="I75" t="s">
+        <v>280</v>
+      </c>
+      <c r="J75" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>282</v>
+      </c>
+      <c r="B76" t="s">
+        <v>36</v>
+      </c>
+      <c r="C76" t="s">
+        <v>60</v>
+      </c>
+      <c r="D76" t="s">
+        <v>13</v>
+      </c>
+      <c r="E76" t="s">
+        <v>142</v>
+      </c>
+      <c r="F76" t="s">
+        <v>88</v>
+      </c>
+      <c r="G76" t="s">
+        <v>143</v>
+      </c>
+      <c r="H76" t="s">
+        <v>17</v>
+      </c>
+      <c r="I76" t="s">
+        <v>283</v>
+      </c>
+      <c r="J76" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>285</v>
+      </c>
+      <c r="B77" t="s">
+        <v>30</v>
+      </c>
+      <c r="C77" t="s">
+        <v>31</v>
+      </c>
+      <c r="D77" t="s">
+        <v>13</v>
+      </c>
+      <c r="E77" t="s">
+        <v>14</v>
+      </c>
+      <c r="F77" t="s">
+        <v>15</v>
+      </c>
+      <c r="G77" t="s">
+        <v>286</v>
+      </c>
+      <c r="H77" t="s">
+        <v>17</v>
+      </c>
+      <c r="I77" t="s">
+        <v>287</v>
+      </c>
+      <c r="J77" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>289</v>
+      </c>
+      <c r="B78" t="s">
+        <v>30</v>
+      </c>
+      <c r="C78" t="s">
+        <v>31</v>
+      </c>
+      <c r="D78" t="s">
+        <v>13</v>
+      </c>
+      <c r="E78" t="s">
+        <v>14</v>
+      </c>
+      <c r="F78" t="s">
+        <v>48</v>
+      </c>
+      <c r="G78" t="s">
+        <v>290</v>
+      </c>
+      <c r="H78" t="s">
+        <v>17</v>
+      </c>
+      <c r="I78" t="s">
+        <v>291</v>
+      </c>
+      <c r="J78" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>293</v>
+      </c>
+      <c r="B79" t="s">
+        <v>36</v>
+      </c>
+      <c r="C79" t="s">
+        <v>60</v>
+      </c>
+      <c r="D79" t="s">
+        <v>13</v>
+      </c>
+      <c r="E79" t="s">
+        <v>14</v>
+      </c>
+      <c r="F79" t="s">
+        <v>15</v>
+      </c>
+      <c r="G79" t="s">
+        <v>44</v>
+      </c>
+      <c r="H79" t="s">
+        <v>17</v>
+      </c>
+      <c r="I79" t="s">
+        <v>294</v>
+      </c>
+      <c r="J79" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>296</v>
+      </c>
+      <c r="B80" t="s">
+        <v>36</v>
+      </c>
+      <c r="C80" t="s">
+        <v>60</v>
+      </c>
+      <c r="D80" t="s">
+        <v>13</v>
+      </c>
+      <c r="E80" t="s">
+        <v>38</v>
+      </c>
+      <c r="F80" t="s">
+        <v>48</v>
+      </c>
+      <c r="G80" t="s">
+        <v>290</v>
+      </c>
+      <c r="H80" t="s">
+        <v>17</v>
+      </c>
+      <c r="I80" t="s">
+        <v>297</v>
+      </c>
+      <c r="J80" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>299</v>
+      </c>
+      <c r="B81" t="s">
+        <v>36</v>
+      </c>
+      <c r="C81" t="s">
+        <v>37</v>
+      </c>
+      <c r="D81" t="s">
+        <v>13</v>
+      </c>
+      <c r="E81" t="s">
+        <v>14</v>
+      </c>
+      <c r="F81" t="s">
+        <v>15</v>
+      </c>
+      <c r="G81" t="s">
+        <v>64</v>
+      </c>
+      <c r="H81" t="s">
+        <v>17</v>
+      </c>
+      <c r="I81" t="s">
+        <v>300</v>
+      </c>
+      <c r="J81" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>302</v>
+      </c>
+      <c r="B82" t="s">
+        <v>36</v>
+      </c>
+      <c r="C82" t="s">
+        <v>60</v>
+      </c>
+      <c r="D82" t="s">
+        <v>13</v>
+      </c>
+      <c r="E82" t="s">
+        <v>38</v>
+      </c>
+      <c r="F82" t="s">
+        <v>15</v>
+      </c>
+      <c r="G82" t="s">
+        <v>39</v>
+      </c>
+      <c r="H82" t="s">
+        <v>17</v>
+      </c>
+      <c r="I82" t="s">
+        <v>303</v>
+      </c>
+      <c r="J82" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>305</v>
+      </c>
+      <c r="B83" t="s">
+        <v>25</v>
+      </c>
+      <c r="C83" t="s">
+        <v>26</v>
+      </c>
+      <c r="D83" t="s">
+        <v>13</v>
+      </c>
+      <c r="E83" t="s">
+        <v>14</v>
+      </c>
+      <c r="F83" t="s">
+        <v>48</v>
+      </c>
+      <c r="G83" t="s">
+        <v>306</v>
+      </c>
+      <c r="H83" t="s">
+        <v>17</v>
+      </c>
+      <c r="I83" t="s">
+        <v>307</v>
+      </c>
+      <c r="J83" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>309</v>
+      </c>
+      <c r="B84" t="s">
+        <v>36</v>
+      </c>
+      <c r="C84" t="s">
+        <v>60</v>
+      </c>
+      <c r="D84" t="s">
+        <v>13</v>
+      </c>
+      <c r="E84" t="s">
+        <v>14</v>
+      </c>
+      <c r="F84" t="s">
+        <v>48</v>
+      </c>
+      <c r="G84" t="s">
+        <v>115</v>
+      </c>
+      <c r="H84" t="s">
+        <v>17</v>
+      </c>
+      <c r="I84" t="s">
+        <v>310</v>
+      </c>
+      <c r="J84" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>312</v>
+      </c>
+      <c r="B85" t="s">
+        <v>36</v>
+      </c>
+      <c r="C85" t="s">
+        <v>60</v>
+      </c>
+      <c r="D85" t="s">
+        <v>13</v>
+      </c>
+      <c r="E85" t="s">
+        <v>14</v>
+      </c>
+      <c r="F85" t="s">
+        <v>15</v>
+      </c>
+      <c r="G85" t="s">
+        <v>64</v>
+      </c>
+      <c r="H85" t="s">
+        <v>17</v>
+      </c>
+      <c r="I85" t="s">
+        <v>155</v>
+      </c>
+      <c r="J85" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>314</v>
+      </c>
+      <c r="B86" t="s">
+        <v>25</v>
+      </c>
+      <c r="C86" t="s">
+        <v>315</v>
+      </c>
+      <c r="D86" t="s">
+        <v>316</v>
+      </c>
+      <c r="E86" t="s">
+        <v>14</v>
+      </c>
+      <c r="F86" t="s">
+        <v>88</v>
+      </c>
+      <c r="G86" t="s">
+        <v>270</v>
+      </c>
+      <c r="H86" t="s">
+        <v>17</v>
+      </c>
+      <c r="I86" t="s">
+        <v>317</v>
+      </c>
+      <c r="J86" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>319</v>
+      </c>
+      <c r="B87" t="s">
+        <v>36</v>
+      </c>
+      <c r="C87" t="s">
+        <v>60</v>
+      </c>
+      <c r="D87" t="s">
+        <v>316</v>
+      </c>
+      <c r="E87" t="s">
+        <v>14</v>
+      </c>
+      <c r="F87" t="s">
+        <v>48</v>
+      </c>
+      <c r="G87" t="s">
+        <v>320</v>
+      </c>
+      <c r="H87" t="s">
+        <v>17</v>
+      </c>
+      <c r="I87" t="s">
+        <v>321</v>
+      </c>
+      <c r="J87" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>323</v>
+      </c>
+      <c r="B88" t="s">
+        <v>30</v>
+      </c>
+      <c r="C88" t="s">
+        <v>84</v>
+      </c>
+      <c r="D88" t="s">
+        <v>13</v>
+      </c>
+      <c r="E88" t="s">
+        <v>142</v>
+      </c>
+      <c r="F88" t="s">
+        <v>88</v>
+      </c>
+      <c r="G88" t="s">
+        <v>143</v>
+      </c>
+      <c r="H88" t="s">
+        <v>17</v>
+      </c>
+      <c r="I88" t="s">
+        <v>324</v>
+      </c>
+      <c r="J88" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="89" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>326</v>
+      </c>
+      <c r="B89" t="s">
+        <v>30</v>
+      </c>
+      <c r="C89" t="s">
+        <v>84</v>
+      </c>
+      <c r="D89" t="s">
+        <v>316</v>
+      </c>
+      <c r="E89" t="s">
+        <v>142</v>
+      </c>
+      <c r="F89" t="s">
+        <v>88</v>
+      </c>
+      <c r="G89" t="s">
+        <v>143</v>
+      </c>
+      <c r="H89" t="s">
+        <v>17</v>
+      </c>
+      <c r="I89" t="s">
+        <v>327</v>
+      </c>
+      <c r="J89" t="s">
+        <v>328</v>
       </c>
     </row>
   </sheetData>
